--- a/Assets/Data/Excel/item.xlsx
+++ b/Assets/Data/Excel/item.xlsx
@@ -513,7 +513,7 @@
     <x:row r="6" ht="28" customHeight="1">
       <x:c r="A6" s="18" t="str"/>
       <x:c r="B6" s="18" t="n">
-        <x:v>101</x:v>
+        <x:v>1000101</x:v>
       </x:c>
       <x:c r="C6" s="18" t="str">
         <x:v>伐木炸弹</x:v>
@@ -549,7 +549,7 @@
     <x:row r="7" ht="28" customHeight="1">
       <x:c r="A7" s="18" t="str"/>
       <x:c r="B7" s="18" t="n">
-        <x:v>102</x:v>
+        <x:v>1000102</x:v>
       </x:c>
       <x:c r="C7" s="18" t="str">
         <x:v>拆桥工具</x:v>
@@ -585,7 +585,7 @@
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="18" t="str"/>
       <x:c r="B8" s="18" t="n">
-        <x:v>201</x:v>
+        <x:v>3000201</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
         <x:v>箭塔图纸</x:v>
@@ -621,7 +621,7 @@
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="18" t="str"/>
       <x:c r="B9" s="18" t="n">
-        <x:v>301</x:v>
+        <x:v>5000301</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
         <x:v>海岛种子</x:v>
@@ -657,7 +657,7 @@
     <x:row r="10" ht="28" customHeight="1">
       <x:c r="A10" s="18" t="str"/>
       <x:c r="B10" s="18" t="n">
-        <x:v>401</x:v>
+        <x:v>4000401</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
         <x:v>黏液核心</x:v>
